--- a/notebooks/solutions/credit_solution.xlsx
+++ b/notebooks/solutions/credit_solution.xlsx
@@ -3879,7 +3879,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3959,16 +3959,16 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>kAcceptedRatio</t>
+          <t>kBadRatio</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Accept</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1</v>
+        <v>0.2212</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
@@ -3982,15 +3982,51 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Reject</t>
+          <t>Accept</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>kAcceptedRatio</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Reject</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>kAcceptedRatio</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>0.4116</v>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
